--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/OREGON_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/OREGON_2021.xlsx
@@ -3138,7 +3138,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C155">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C163">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C576">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C611">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C612">
